--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260702.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260702.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.11%</t>
+          <t>10.00%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.66%</t>
+          <t>8.98%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.38%</t>
+          <t>8.60%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.37%</t>
+          <t>7.42%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>5.91%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.38%</t>
+          <t>5.86%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.34%</t>
+          <t>5.05%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.94%</t>
+          <t>4.86%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.82%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.26%</t>
         </is>
       </c>
     </row>
@@ -836,51 +836,51 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>3.75%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>8,949,000</t>
+          <t>8,315,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.48%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>8,315,000</t>
+          <t>8,949,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.47%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1073,34 +1073,34 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>636,000</t>
+          <t>457,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,334,000</t>
+          <t>3,808,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1122,29 +1122,29 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>3,808,000</t>
+          <t>1,334,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1166,95 +1166,95 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>416,000</t>
+          <t>4,334,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>4,334,000</t>
+          <t>2,966,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,966,000</t>
+          <t>530,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>530,000</t>
+          <t>291,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
@@ -1276,24 +1276,24 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>1,508,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,127 +1305,127 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,508,000</t>
+          <t>1,741,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,741,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>490,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.02%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>8,658,029,313</t>
+          <t>10,128,869,928</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>3,885,980,027</t>
+          <t>3,875,967,632</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
